--- a/outputs/52050.xlsx
+++ b/outputs/52050.xlsx
@@ -173,28 +173,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -390,2217 +394,2217 @@
   <dimension ref="A1:BE14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="4" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="4" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
-      <c r="BC1" s="1"/>
-      <c r="BE1" s="0" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2"/>
+      <c r="BA1" s="2"/>
+      <c r="BB1" s="2"/>
+      <c r="BC1" s="2"/>
+      <c r="BE1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
-      </c>
-      <c r="B2" s="0" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="S2" s="3" t="n">
+      <c r="S2" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="T2" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="X2" s="3" t="n">
+      <c r="X2" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="Z2" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AA2" s="3" t="n">
+      <c r="AA2" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AB2" s="3" t="n">
+      <c r="AB2" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AD2" s="3" t="n">
+      <c r="AD2" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AE2" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" s="3" t="n">
+      <c r="AE2" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF2" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="AG2" s="3" t="n">
+      <c r="AG2" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="AH2" s="4" t="n">
+      <c r="AH2" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AI2" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AJ2" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AK2" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AL2" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AM2" s="3" t="n">
+      <c r="AM2" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AN2" s="3" t="n">
+      <c r="AN2" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AO2" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AP2" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AQ2" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="AR2" s="3" t="n">
+      <c r="AR2" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="AS2" s="3" t="n">
+      <c r="AS2" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="AT2" s="3" t="n">
+      <c r="AT2" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AU2" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="AV2" s="3" t="n">
+      <c r="AV2" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AW2" s="3" t="n">
+      <c r="AW2" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="AX2" s="3" t="n">
+      <c r="AX2" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="AY2" s="3" t="n">
+      <c r="AY2" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="AZ2" s="3" t="n">
+      <c r="AZ2" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="BA2" s="3" t="n">
+      <c r="BA2" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="BB2" s="3" t="n">
+      <c r="BB2" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="BC2" s="3" t="n">
+      <c r="BC2" s="4" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="L3" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="M3" s="0" t="n">
+      <c r="L3" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="Q3" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="T3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="U3" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="V3" s="0" t="n">
+      <c r="U3" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="V3" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="W3" s="0" t="n">
+      <c r="W3" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="X3" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="0" t="n">
+      <c r="X3" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="Z3" s="0" t="n">
+      <c r="Z3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AA3" s="0" t="n">
+      <c r="AA3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AB3" s="0" t="n">
+      <c r="AB3" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AC3" s="0" t="n">
+      <c r="AC3" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AD3" s="0" t="n">
+      <c r="AD3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AE3" s="0" t="n">
+      <c r="AE3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AF3" s="0" t="n">
+      <c r="AF3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AH3" s="5" t="n">
+      <c r="AH3" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="AI3" s="0" t="n">
+      <c r="AI3" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AJ3" s="0" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AK3" s="0" t="n">
+      <c r="AK3" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AL3" s="0" t="n">
+      <c r="AL3" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AM3" s="0" t="n">
+      <c r="AM3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AN3" s="0" t="n">
+      <c r="AN3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AO3" s="0" t="n">
+      <c r="AO3" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AP3" s="0" t="n">
+      <c r="AP3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AQ3" s="0" t="n">
+      <c r="AQ3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AR3" s="0" t="n">
+      <c r="AR3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AS3" s="0" t="n">
+      <c r="AS3" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AT3" s="0" t="n">
+      <c r="AT3" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AU3" s="0" t="n">
+      <c r="AU3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AV3" s="0" t="n">
+      <c r="AV3" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="AW3" s="0" t="n">
+      <c r="AW3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AX3" s="0" t="n">
+      <c r="AX3" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="AY3" s="0" t="n">
+      <c r="AY3" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AZ3" s="0" t="n">
+      <c r="AZ3" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="BA3" s="0" t="n">
+      <c r="BA3" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="BB3" s="0" t="n">
+      <c r="BB3" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="BC3" s="0" t="n">
+      <c r="BC3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BE3" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D3:BC3)</f>
+      <c r="BE3" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D3:BC3)</f>
         <v>531</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="T4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="U4" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="0" t="n">
+      <c r="W4" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="X4" s="0" t="n">
+      <c r="X4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="Y4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" s="0" t="n">
+      <c r="Z4" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AA4" s="0" t="n">
+      <c r="AA4" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AB4" s="0" t="n">
+      <c r="AB4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AC4" s="0" t="n">
+      <c r="AC4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AD4" s="0" t="n">
+      <c r="AD4" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AF4" s="0" t="n">
+      <c r="AF4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AH4" s="5" t="n">
+      <c r="AH4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="AI4" s="0" t="n">
+      <c r="AI4" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="AK4" s="0" t="n">
+      <c r="AK4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AL4" s="0" t="n">
+      <c r="AL4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AM4" s="0" t="n">
+      <c r="AM4" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AN4" s="0" t="n">
+      <c r="AN4" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AO4" s="0" t="n">
+      <c r="AO4" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AP4" s="0" t="n">
+      <c r="AP4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AQ4" s="0" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AR4" s="0" t="n">
+      <c r="AR4" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AS4" s="0" t="n">
+      <c r="AS4" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AT4" s="0" t="n">
+      <c r="AT4" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AU4" s="0" t="n">
+      <c r="AU4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AV4" s="0" t="n">
+      <c r="AV4" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AW4" s="0" t="n">
+      <c r="AW4" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AX4" s="0" t="n">
+      <c r="AX4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AY4" s="0" t="n">
+      <c r="AY4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AZ4" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA4" s="0" t="n">
+      <c r="AZ4" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="BB4" s="0" t="n">
+      <c r="BB4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="BC4" s="0" t="n">
+      <c r="BC4" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="BE4" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D4:BC4)</f>
+      <c r="BE4" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D4:BC4)</f>
         <v>439</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="F5" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="T5" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="U5" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="W5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="X5" s="0" t="n">
+      <c r="X5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="Y5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Z5" s="0" t="n">
+      <c r="Z5" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="AA5" s="0" t="n">
+      <c r="AA5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="0" t="n">
+      <c r="AC5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="AD5" s="0" t="n">
+      <c r="AD5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" s="0" t="n">
+      <c r="AF5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AG5" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AH5" s="5" t="n">
+      <c r="AH5" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="AI5" s="0" t="n">
+      <c r="AI5" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AJ5" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" s="0" t="n">
+      <c r="AJ5" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AL5" s="0" t="n">
+      <c r="AL5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AM5" s="0" t="n">
+      <c r="AM5" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AN5" s="0" t="n">
+      <c r="AN5" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="AO5" s="0" t="n">
+      <c r="AO5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AP5" s="0" t="n">
+      <c r="AP5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AQ5" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR5" s="0" t="n">
+      <c r="AQ5" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR5" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AS5" s="0" t="n">
+      <c r="AS5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AT5" s="0" t="n">
+      <c r="AT5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AU5" s="0" t="n">
+      <c r="AU5" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AV5" s="0" t="n">
+      <c r="AV5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AW5" s="0" t="n">
+      <c r="AW5" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AX5" s="0" t="n">
+      <c r="AX5" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AY5" s="0" t="n">
+      <c r="AY5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AZ5" s="0" t="n">
+      <c r="AZ5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="BA5" s="0" t="n">
+      <c r="BA5" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="BB5" s="0" t="n">
+      <c r="BB5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="BC5" s="0" t="n">
+      <c r="BC5" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="BE5" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D5:BC5)</f>
+      <c r="BE5" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D5:BC5)</f>
         <v>503</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="U6" s="0" t="n">
+      <c r="U6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="X6" s="0" t="n">
+      <c r="X6" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="Y6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="0" t="n">
+      <c r="Z6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AA6" s="0" t="n">
+      <c r="AA6" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="AB6" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AC6" s="0" t="n">
+      <c r="AC6" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AD6" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AF6" s="0" t="n">
+      <c r="AF6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AH6" s="5" t="n">
+      <c r="AH6" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="AI6" s="0" t="n">
+      <c r="AI6" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="AJ6" s="0" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="AK6" s="0" t="n">
+      <c r="AK6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AL6" s="0" t="n">
+      <c r="AL6" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AM6" s="0" t="n">
+      <c r="AM6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AN6" s="0" t="n">
+      <c r="AN6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AO6" s="0" t="n">
+      <c r="AO6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AP6" s="0" t="n">
+      <c r="AP6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AQ6" s="0" t="n">
+      <c r="AQ6" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AR6" s="0" t="n">
+      <c r="AR6" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AS6" s="0" t="n">
+      <c r="AS6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AT6" s="0" t="n">
+      <c r="AT6" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AU6" s="0" t="n">
+      <c r="AU6" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AV6" s="0" t="n">
+      <c r="AV6" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AW6" s="0" t="n">
+      <c r="AW6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AX6" s="0" t="n">
+      <c r="AX6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AY6" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ6" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA6" s="0" t="n">
+      <c r="AY6" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ6" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="BB6" s="0" t="n">
+      <c r="BB6" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="BC6" s="0" t="n">
+      <c r="BC6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="BE6" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D6:BC6)</f>
+      <c r="BE6" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D6:BC6)</f>
         <v>400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="N7" s="0" t="n">
+      <c r="M7" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T7" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="U7" s="0" t="n">
+      <c r="T7" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="W7" s="0" t="n">
+      <c r="W7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="X7" s="0" t="n">
+      <c r="X7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="Z7" s="0" t="n">
+      <c r="Z7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AA7" s="0" t="n">
+      <c r="AA7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="AB7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="AC7" s="0" t="n">
+      <c r="AC7" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AD7" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AF7" s="0" t="n">
+      <c r="AF7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH7" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI7" s="0" t="n">
+      <c r="AH7" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AJ7" s="0" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AK7" s="0" t="n">
+      <c r="AK7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AL7" s="0" t="n">
+      <c r="AL7" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AM7" s="0" t="n">
+      <c r="AM7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AN7" s="0" t="n">
+      <c r="AN7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AO7" s="0" t="n">
+      <c r="AO7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AP7" s="0" t="n">
+      <c r="AP7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AQ7" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR7" s="0" t="n">
+      <c r="AQ7" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR7" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AS7" s="0" t="n">
+      <c r="AS7" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="AT7" s="0" t="n">
+      <c r="AT7" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AU7" s="0" t="n">
+      <c r="AU7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AV7" s="0" t="n">
+      <c r="AV7" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AW7" s="0" t="n">
+      <c r="AW7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AX7" s="0" t="n">
+      <c r="AX7" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AY7" s="0" t="n">
+      <c r="AY7" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AZ7" s="0" t="n">
+      <c r="AZ7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="BA7" s="0" t="n">
+      <c r="BA7" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="BB7" s="0" t="n">
+      <c r="BB7" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BC7" s="0" t="n">
+      <c r="BC7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BE7" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D7:BC7)</f>
+      <c r="BE7" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D7:BC7)</f>
         <v>424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="0" t="n">
+      <c r="E8" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="K8" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="L8" s="0" t="n">
+      <c r="K8" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="T8" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="U8" s="0" t="n">
+      <c r="T8" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="W8" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="X8" s="0" t="n">
+      <c r="X8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="Y8" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="Z8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AA8" s="0" t="n">
+      <c r="AA8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="AB8" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AC8" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AD8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AF8" s="0" t="n">
+      <c r="AF8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AG8" s="0" t="n">
+      <c r="AG8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AH8" s="5" t="n">
+      <c r="AH8" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="AI8" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="AJ8" s="0" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AK8" s="0" t="n">
+      <c r="AK8" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AL8" s="0" t="n">
+      <c r="AL8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM8" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AN8" s="0" t="n">
+      <c r="AM8" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN8" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AO8" s="0" t="n">
+      <c r="AO8" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AP8" s="0" t="n">
+      <c r="AP8" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="AQ8" s="0" t="n">
+      <c r="AQ8" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AR8" s="0" t="n">
+      <c r="AR8" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="AS8" s="0" t="n">
+      <c r="AS8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AT8" s="0" t="n">
+      <c r="AT8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AU8" s="0" t="n">
+      <c r="AU8" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AV8" s="0" t="n">
+      <c r="AV8" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AW8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AX8" s="0" t="n">
+      <c r="AX8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AY8" s="0" t="n">
+      <c r="AY8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AZ8" s="0" t="n">
+      <c r="AZ8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="BA8" s="0" t="n">
+      <c r="BA8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BB8" s="0" t="n">
+      <c r="BB8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="BC8" s="0" t="n">
+      <c r="BC8" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="BE8" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D8:BC8)</f>
+      <c r="BE8" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D8:BC8)</f>
         <v>445</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="T9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="U9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="W9" s="0" t="n">
+      <c r="W9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="X9" s="0" t="n">
+      <c r="X9" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="Y9" s="0" t="n">
+      <c r="Y9" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="Z9" s="0" t="n">
+      <c r="Z9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AA9" s="0" t="n">
+      <c r="AA9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AB9" s="0" t="n">
+      <c r="AB9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AC9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AD9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AF9" s="0" t="n">
+      <c r="AF9" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AG9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="AH9" s="5" t="n">
+      <c r="AH9" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="AI9" s="0" t="n">
+      <c r="AI9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AJ9" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK9" s="0" t="n">
+      <c r="AJ9" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AL9" s="0" t="n">
+      <c r="AL9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AM9" s="0" t="n">
+      <c r="AM9" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AN9" s="0" t="n">
+      <c r="AN9" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AO9" s="0" t="n">
+      <c r="AO9" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AP9" s="0" t="n">
+      <c r="AP9" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AQ9" s="0" t="n">
+      <c r="AQ9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AR9" s="0" t="n">
+      <c r="AR9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AS9" s="0" t="n">
+      <c r="AS9" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AT9" s="0" t="n">
+      <c r="AT9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AU9" s="0" t="n">
+      <c r="AU9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AV9" s="0" t="n">
+      <c r="AV9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AW9" s="0" t="n">
+      <c r="AW9" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AX9" s="0" t="n">
+      <c r="AX9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AY9" s="0" t="n">
+      <c r="AY9" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AZ9" s="0" t="n">
+      <c r="AZ9" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="BA9" s="0" t="n">
+      <c r="BA9" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="BB9" s="0" t="n">
+      <c r="BB9" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="BC9" s="0" t="n">
+      <c r="BC9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="BE9" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D9:BC9)</f>
+      <c r="BE9" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D9:BC9)</f>
         <v>470</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="K10" s="0" t="n">
+      <c r="J10" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="S10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T10" s="0" t="n">
+      <c r="T10" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="U10" s="0" t="n">
+      <c r="U10" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="W10" s="0" t="n">
+      <c r="W10" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="X10" s="0" t="n">
+      <c r="X10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="0" t="n">
+      <c r="Y10" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="Z10" s="0" t="n">
+      <c r="Z10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AA10" s="0" t="n">
+      <c r="AA10" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AB10" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC10" s="0" t="n">
+      <c r="AB10" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AD10" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AF10" s="0" t="n">
+      <c r="AF10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AG10" s="0" t="n">
+      <c r="AG10" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AH10" s="5" t="n">
+      <c r="AH10" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="AI10" s="0" t="n">
+      <c r="AI10" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AK10" s="0" t="n">
+      <c r="AK10" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AL10" s="0" t="n">
+      <c r="AL10" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AM10" s="0" t="n">
+      <c r="AM10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AN10" s="0" t="n">
+      <c r="AN10" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AO10" s="0" t="n">
+      <c r="AO10" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AP10" s="0" t="n">
+      <c r="AP10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AQ10" s="0" t="n">
+      <c r="AQ10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AR10" s="0" t="n">
+      <c r="AR10" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AS10" s="0" t="n">
+      <c r="AS10" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AT10" s="0" t="n">
+      <c r="AT10" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AU10" s="0" t="n">
+      <c r="AU10" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AV10" s="0" t="n">
+      <c r="AV10" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AW10" s="0" t="n">
+      <c r="AW10" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AX10" s="0" t="n">
+      <c r="AX10" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AY10" s="0" t="n">
+      <c r="AY10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AZ10" s="0" t="n">
+      <c r="AZ10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="BA10" s="0" t="n">
+      <c r="BA10" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="BB10" s="0" t="n">
+      <c r="BB10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="BC10" s="0" t="n">
+      <c r="BC10" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="BE10" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D10:BC10)</f>
+      <c r="BE10" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D10:BC10)</f>
         <v>433</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="Q11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="T11" s="0" t="n">
+      <c r="T11" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="U11" s="0" t="n">
+      <c r="U11" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="W11" s="0" t="n">
+      <c r="W11" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="X11" s="0" t="n">
+      <c r="X11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Y11" s="0" t="n">
+      <c r="Y11" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Z11" s="0" t="n">
+      <c r="Z11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="AA11" s="0" t="n">
+      <c r="AA11" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AB11" s="0" t="n">
+      <c r="AB11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="AC11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AD11" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AF11" s="0" t="n">
+      <c r="AF11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AG11" s="0" t="n">
+      <c r="AG11" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AH11" s="5" t="n">
+      <c r="AH11" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="AI11" s="0" t="n">
+      <c r="AI11" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AJ11" s="0" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AK11" s="0" t="n">
+      <c r="AK11" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AL11" s="0" t="n">
+      <c r="AL11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AM11" s="0" t="n">
+      <c r="AM11" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AN11" s="0" t="n">
+      <c r="AN11" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="AO11" s="0" t="n">
+      <c r="AO11" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AP11" s="0" t="n">
+      <c r="AP11" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AQ11" s="0" t="n">
+      <c r="AQ11" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AR11" s="0" t="n">
+      <c r="AR11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AS11" s="0" t="n">
+      <c r="AS11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AT11" s="0" t="n">
+      <c r="AT11" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AU11" s="0" t="n">
+      <c r="AU11" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AV11" s="0" t="n">
+      <c r="AV11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AW11" s="0" t="n">
+      <c r="AW11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AX11" s="0" t="n">
+      <c r="AX11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AY11" s="0" t="n">
+      <c r="AY11" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="AZ11" s="0" t="n">
+      <c r="AZ11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="BA11" s="0" t="n">
+      <c r="BA11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BB11" s="0" t="n">
+      <c r="BB11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" s="0" t="n">
+      <c r="BC11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BE11" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D11:BC11)</f>
+      <c r="BE11" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D11:BC11)</f>
         <v>477</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="H12" s="0" t="n">
+      <c r="G12" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" s="0" t="n">
+      <c r="Q12" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="R12" s="0" t="n">
+      <c r="R12" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S12" s="0" t="n">
+      <c r="S12" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="T12" s="0" t="n">
+      <c r="T12" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="U12" s="0" t="n">
+      <c r="U12" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="V12" s="0" t="n">
+      <c r="V12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W12" s="0" t="n">
+      <c r="W12" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="X12" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y12" s="0" t="n">
+      <c r="X12" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Z12" s="0" t="n">
+      <c r="Z12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AA12" s="0" t="n">
+      <c r="AA12" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AB12" s="0" t="n">
+      <c r="AB12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AC12" s="0" t="n">
+      <c r="AC12" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AD12" s="0" t="n">
+      <c r="AD12" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AE12" s="0" t="n">
+      <c r="AE12" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AF12" s="0" t="n">
+      <c r="AF12" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AG12" s="0" t="n">
+      <c r="AG12" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="AH12" s="5" t="n">
+      <c r="AH12" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="AI12" s="0" t="n">
+      <c r="AI12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AJ12" s="0" t="n">
+      <c r="AJ12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AK12" s="0" t="n">
+      <c r="AK12" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AL12" s="0" t="n">
+      <c r="AL12" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AM12" s="0" t="n">
+      <c r="AM12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AN12" s="0" t="n">
+      <c r="AN12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AO12" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP12" s="0" t="n">
+      <c r="AO12" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP12" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AQ12" s="0" t="n">
+      <c r="AQ12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AR12" s="0" t="n">
+      <c r="AR12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AS12" s="0" t="n">
+      <c r="AS12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AT12" s="0" t="n">
+      <c r="AT12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AU12" s="0" t="n">
+      <c r="AU12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AV12" s="0" t="n">
+      <c r="AV12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW12" s="0" t="n">
+      <c r="AW12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AX12" s="0" t="n">
+      <c r="AX12" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AY12" s="0" t="n">
+      <c r="AY12" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AZ12" s="0" t="n">
+      <c r="AZ12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="BA12" s="0" t="n">
+      <c r="BA12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="BB12" s="0" t="n">
+      <c r="BB12" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="BC12" s="0" t="n">
+      <c r="BC12" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="BE12" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D12:BC12)</f>
+      <c r="BE12" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D12:BC12)</f>
         <v>305</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="E13" s="0" t="n">
+      <c r="D13" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O13" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="P13" s="0" t="n">
+      <c r="O13" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" s="0" t="n">
+      <c r="Q13" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="R13" s="0" t="n">
+      <c r="R13" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="S13" s="0" t="n">
+      <c r="S13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="T13" s="0" t="n">
+      <c r="T13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U13" s="0" t="n">
+      <c r="U13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="0" t="n">
+      <c r="V13" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="W13" s="0" t="n">
+      <c r="W13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="X13" s="0" t="n">
+      <c r="X13" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="Y13" s="0" t="n">
+      <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" s="0" t="n">
+      <c r="Z13" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AA13" s="0" t="n">
+      <c r="AA13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AB13" s="0" t="n">
+      <c r="AB13" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AC13" s="0" t="n">
+      <c r="AC13" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="AD13" s="0" t="n">
+      <c r="AD13" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AE13" s="0" t="n">
+      <c r="AE13" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AF13" s="0" t="n">
+      <c r="AF13" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AG13" s="0" t="n">
+      <c r="AG13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AH13" s="5" t="n">
+      <c r="AH13" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="AI13" s="0" t="n">
+      <c r="AI13" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="AJ13" s="0" t="n">
+      <c r="AJ13" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="AK13" s="0" t="n">
+      <c r="AK13" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AL13" s="0" t="n">
+      <c r="AL13" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AM13" s="0" t="n">
+      <c r="AM13" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AN13" s="0" t="n">
+      <c r="AN13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AO13" s="0" t="n">
+      <c r="AO13" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AP13" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ13" s="0" t="n">
+      <c r="AP13" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AR13" s="0" t="n">
+      <c r="AR13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AS13" s="0" t="n">
+      <c r="AS13" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AT13" s="0" t="n">
+      <c r="AT13" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AU13" s="0" t="n">
+      <c r="AU13" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="AV13" s="0" t="n">
+      <c r="AV13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW13" s="0" t="n">
+      <c r="AW13" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AX13" s="0" t="n">
+      <c r="AX13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AY13" s="0" t="n">
+      <c r="AY13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AZ13" s="0" t="n">
+      <c r="AZ13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="BA13" s="0" t="n">
+      <c r="BA13" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="BB13" s="0" t="n">
+      <c r="BB13" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="BC13" s="0" t="n">
+      <c r="BC13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="BE13" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D13:BC13)</f>
+      <c r="BE13" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D13:BC13)</f>
         <v>463</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="I14" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="Q14" s="0" t="n">
+      <c r="Q14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="S14" s="0" t="n">
+      <c r="S14" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="T14" s="0" t="n">
+      <c r="T14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U14" s="0" t="n">
+      <c r="U14" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="V14" s="0" t="n">
+      <c r="V14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W14" s="0" t="n">
+      <c r="W14" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="X14" s="0" t="n">
+      <c r="X14" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="Y14" s="0" t="n">
+      <c r="Y14" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="Z14" s="0" t="n">
+      <c r="Z14" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="AA14" s="0" t="n">
+      <c r="AA14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AB14" s="0" t="n">
+      <c r="AB14" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AC14" s="0" t="n">
+      <c r="AC14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AD14" s="0" t="n">
+      <c r="AD14" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AE14" s="0" t="n">
+      <c r="AE14" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="0" t="n">
+      <c r="AF14" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AG14" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH14" s="5" t="n">
+      <c r="AG14" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH14" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="AI14" s="0" t="n">
+      <c r="AI14" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AJ14" s="0" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AK14" s="0" t="n">
+      <c r="AK14" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AL14" s="0" t="n">
+      <c r="AL14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AM14" s="0" t="n">
+      <c r="AM14" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AN14" s="0" t="n">
+      <c r="AN14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AO14" s="0" t="n">
+      <c r="AO14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AP14" s="0" t="n">
+      <c r="AP14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AQ14" s="0" t="n">
+      <c r="AQ14" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AR14" s="0" t="n">
+      <c r="AR14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AS14" s="0" t="n">
+      <c r="AS14" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="AT14" s="0" t="n">
+      <c r="AT14" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AU14" s="0" t="n">
+      <c r="AU14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV14" s="0" t="n">
+      <c r="AV14" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="AW14" s="0" t="n">
+      <c r="AW14" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="AX14" s="0" t="n">
+      <c r="AX14" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="AY14" s="0" t="n">
+      <c r="AY14" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AZ14" s="0" t="n">
+      <c r="AZ14" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="BA14" s="0" t="n">
+      <c r="BA14" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="BB14" s="0" t="n">
+      <c r="BB14" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="BC14" s="0" t="n">
+      <c r="BC14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="BE14" s="0" t="n">
-        <f aca="false">SUMPRODUCT((D$2:BC$2&gt;=$B$2)*D14:BC14)</f>
+      <c r="BE14" s="1" t="n">
+        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D14:BC14)</f>
         <v>441</v>
       </c>
     </row>

--- a/outputs/52050.xlsx
+++ b/outputs/52050.xlsx
@@ -1,113 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97342\Desktop\130_excel公式已检查\52050\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA641D1E-585A-4355-A9F0-ECF133EA13B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="19406" windowHeight="11606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t xml:space="preserve">Date</t>
+    <t>Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Week no.</t>
+    <t>Week no.</t>
   </si>
   <si>
-    <t xml:space="preserve">Weeks</t>
+    <t>Weeks</t>
   </si>
   <si>
-    <t xml:space="preserve">Total from this week</t>
+    <t>Total from this week</t>
   </si>
   <si>
-    <t xml:space="preserve">a</t>
+    <t>a</t>
   </si>
   <si>
-    <t xml:space="preserve">b</t>
+    <t>b</t>
   </si>
   <si>
-    <t xml:space="preserve">c</t>
+    <t>c</t>
   </si>
   <si>
-    <t xml:space="preserve">d</t>
+    <t>d</t>
   </si>
   <si>
-    <t xml:space="preserve">e</t>
+    <t>e</t>
   </si>
   <si>
-    <t xml:space="preserve">f</t>
+    <t>f</t>
   </si>
   <si>
-    <t xml:space="preserve">g</t>
+    <t>g</t>
   </si>
   <si>
-    <t xml:space="preserve">h</t>
+    <t>h</t>
   </si>
   <si>
-    <t xml:space="preserve">i</t>
+    <t>i</t>
   </si>
   <si>
-    <t xml:space="preserve">j</t>
+    <t>j</t>
   </si>
   <si>
-    <t xml:space="preserve">k</t>
+    <t>k</t>
   </si>
   <si>
-    <t xml:space="preserve">l</t>
+    <t>l</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,110 +108,81 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -257,55 +217,119 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -313,24 +337,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -343,7 +376,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -353,13 +392,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -367,6 +408,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -374,2250 +416,2214 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="4" style="1" width="3"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="4" max="55" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2"/>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
-      <c r="BC1" s="2"/>
-      <c r="BE1" s="1" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="5"/>
+      <c r="AY1" s="5"/>
+      <c r="AZ1" s="5"/>
+      <c r="BA1" s="5"/>
+      <c r="BB1" s="5"/>
+      <c r="BC1" s="5"/>
+      <c r="BE1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <f aca="true">TODAY()</f>
-        <v>46271</v>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <f ca="1">TODAY()</f>
+        <v>45443</v>
+      </c>
+      <c r="B2">
         <v>31</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="2">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="2">
         <v>3</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2">
         <v>4</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="2">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="2">
         <v>6</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="2">
         <v>7</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="2">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="2">
         <v>9</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="2">
         <v>10</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="2">
         <v>11</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="2">
         <v>12</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="2">
         <v>13</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="2">
         <v>14</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="2">
         <v>15</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="S2" s="2">
         <v>16</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="2">
         <v>17</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="2">
         <v>18</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="2">
         <v>19</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="2">
         <v>20</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="X2" s="2">
         <v>21</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Y2" s="2">
         <v>22</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="Z2" s="2">
         <v>23</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AA2" s="2">
         <v>24</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="2">
         <v>25</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="2">
         <v>26</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AD2" s="2">
         <v>27</v>
       </c>
-      <c r="AE2" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AE2" s="2">
+        <v>28</v>
+      </c>
+      <c r="AF2" s="2">
         <v>29</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AG2" s="2">
         <v>30</v>
       </c>
-      <c r="AH2" s="5" t="n">
+      <c r="AH2" s="3">
         <v>31</v>
       </c>
-      <c r="AI2" s="4" t="n">
+      <c r="AI2" s="2">
         <v>32</v>
       </c>
-      <c r="AJ2" s="4" t="n">
+      <c r="AJ2" s="2">
         <v>33</v>
       </c>
-      <c r="AK2" s="4" t="n">
+      <c r="AK2" s="2">
         <v>34</v>
       </c>
-      <c r="AL2" s="4" t="n">
+      <c r="AL2" s="2">
         <v>35</v>
       </c>
-      <c r="AM2" s="4" t="n">
+      <c r="AM2" s="2">
         <v>36</v>
       </c>
-      <c r="AN2" s="4" t="n">
+      <c r="AN2" s="2">
         <v>37</v>
       </c>
-      <c r="AO2" s="4" t="n">
+      <c r="AO2" s="2">
         <v>38</v>
       </c>
-      <c r="AP2" s="4" t="n">
+      <c r="AP2" s="2">
         <v>39</v>
       </c>
-      <c r="AQ2" s="4" t="n">
+      <c r="AQ2" s="2">
         <v>40</v>
       </c>
-      <c r="AR2" s="4" t="n">
+      <c r="AR2" s="2">
         <v>41</v>
       </c>
-      <c r="AS2" s="4" t="n">
+      <c r="AS2" s="2">
         <v>42</v>
       </c>
-      <c r="AT2" s="4" t="n">
+      <c r="AT2" s="2">
         <v>43</v>
       </c>
-      <c r="AU2" s="4" t="n">
+      <c r="AU2" s="2">
         <v>44</v>
       </c>
-      <c r="AV2" s="4" t="n">
+      <c r="AV2" s="2">
         <v>45</v>
       </c>
-      <c r="AW2" s="4" t="n">
+      <c r="AW2" s="2">
         <v>46</v>
       </c>
-      <c r="AX2" s="4" t="n">
+      <c r="AX2" s="2">
         <v>47</v>
       </c>
-      <c r="AY2" s="4" t="n">
+      <c r="AY2" s="2">
         <v>48</v>
       </c>
-      <c r="AZ2" s="4" t="n">
+      <c r="AZ2" s="2">
         <v>49</v>
       </c>
-      <c r="BA2" s="4" t="n">
+      <c r="BA2" s="2">
         <v>50</v>
       </c>
-      <c r="BB2" s="4" t="n">
+      <c r="BB2" s="2">
         <v>51</v>
       </c>
-      <c r="BC2" s="4" t="n">
+      <c r="BC2" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3">
         <v>31</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3">
         <v>17</v>
       </c>
-      <c r="L3" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="M3" s="1" t="n">
+      <c r="L3">
+        <v>28</v>
+      </c>
+      <c r="M3">
         <v>11</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3">
         <v>16</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3">
         <v>16</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="P3">
         <v>26</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="Q3">
         <v>18</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3">
         <v>37</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="S3">
         <v>17</v>
       </c>
-      <c r="T3" s="1" t="n">
+      <c r="T3">
         <v>8</v>
       </c>
-      <c r="U3" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="V3" s="1" t="n">
+      <c r="U3">
+        <v>28</v>
+      </c>
+      <c r="V3">
         <v>35</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="W3">
         <v>15</v>
       </c>
-      <c r="X3" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="1" t="n">
+      <c r="X3">
+        <v>28</v>
+      </c>
+      <c r="Y3">
         <v>13</v>
       </c>
-      <c r="Z3" s="1" t="n">
+      <c r="Z3">
         <v>8</v>
       </c>
-      <c r="AA3" s="1" t="n">
+      <c r="AA3">
         <v>6</v>
       </c>
-      <c r="AB3" s="1" t="n">
+      <c r="AB3">
         <v>14</v>
       </c>
-      <c r="AC3" s="1" t="n">
+      <c r="AC3">
         <v>21</v>
       </c>
-      <c r="AD3" s="1" t="n">
+      <c r="AD3">
         <v>7</v>
       </c>
-      <c r="AE3" s="1" t="n">
+      <c r="AE3">
         <v>8</v>
       </c>
-      <c r="AF3" s="1" t="n">
+      <c r="AF3">
         <v>7</v>
       </c>
-      <c r="AG3" s="1" t="n">
+      <c r="AG3">
         <v>10</v>
       </c>
-      <c r="AH3" s="6" t="n">
+      <c r="AH3" s="4">
         <v>26</v>
       </c>
-      <c r="AI3" s="1" t="n">
+      <c r="AI3">
         <v>27</v>
       </c>
-      <c r="AJ3" s="1" t="n">
+      <c r="AJ3">
         <v>40</v>
       </c>
-      <c r="AK3" s="1" t="n">
+      <c r="AK3">
         <v>24</v>
       </c>
-      <c r="AL3" s="1" t="n">
+      <c r="AL3">
         <v>39</v>
       </c>
-      <c r="AM3" s="1" t="n">
+      <c r="AM3">
         <v>40</v>
       </c>
-      <c r="AN3" s="1" t="n">
+      <c r="AN3">
         <v>3</v>
       </c>
-      <c r="AO3" s="1" t="n">
+      <c r="AO3">
         <v>11</v>
       </c>
-      <c r="AP3" s="1" t="n">
+      <c r="AP3">
         <v>9</v>
       </c>
-      <c r="AQ3" s="1" t="n">
+      <c r="AQ3">
         <v>7</v>
       </c>
-      <c r="AR3" s="1" t="n">
+      <c r="AR3">
         <v>40</v>
       </c>
-      <c r="AS3" s="1" t="n">
+      <c r="AS3">
         <v>26</v>
       </c>
-      <c r="AT3" s="1" t="n">
+      <c r="AT3">
         <v>21</v>
       </c>
-      <c r="AU3" s="1" t="n">
+      <c r="AU3">
         <v>12</v>
       </c>
-      <c r="AV3" s="1" t="n">
+      <c r="AV3">
         <v>37</v>
       </c>
-      <c r="AW3" s="1" t="n">
+      <c r="AW3">
         <v>30</v>
       </c>
-      <c r="AX3" s="1" t="n">
+      <c r="AX3">
         <v>29</v>
       </c>
-      <c r="AY3" s="1" t="n">
+      <c r="AY3">
         <v>16</v>
       </c>
-      <c r="AZ3" s="1" t="n">
+      <c r="AZ3">
         <v>20</v>
       </c>
-      <c r="BA3" s="1" t="n">
+      <c r="BA3">
         <v>39</v>
       </c>
-      <c r="BB3" s="1" t="n">
+      <c r="BB3">
         <v>33</v>
       </c>
-      <c r="BC3" s="1" t="n">
+      <c r="BC3">
         <v>2</v>
       </c>
-      <c r="BE3" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D3:BC3)</f>
+      <c r="BE3">
         <v>531</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4">
         <v>23</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4">
         <v>39</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4">
         <v>34</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4">
         <v>5</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4">
         <v>6</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4">
         <v>16</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4">
         <v>24</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4">
         <v>31</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4">
         <v>19</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="P4">
         <v>17</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="Q4">
         <v>1</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4">
         <v>35</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="S4">
         <v>10</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="T4">
         <v>30</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="U4">
         <v>39</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="V4">
         <v>0</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="W4">
         <v>37</v>
       </c>
-      <c r="X4" s="1" t="n">
+      <c r="X4">
         <v>7</v>
       </c>
-      <c r="Y4" s="1" t="n">
+      <c r="Y4">
         <v>12</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="Z4">
         <v>11</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AA4">
         <v>14</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AB4">
         <v>30</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AC4">
         <v>19</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AD4">
         <v>34</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="AE4">
         <v>12</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="AF4">
         <v>10</v>
       </c>
-      <c r="AG4" s="1" t="n">
+      <c r="AG4">
         <v>10</v>
       </c>
-      <c r="AH4" s="6" t="n">
+      <c r="AH4" s="4">
         <v>18</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="AI4">
         <v>33</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="AJ4">
         <v>38</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="AK4">
         <v>8</v>
       </c>
-      <c r="AL4" s="1" t="n">
+      <c r="AL4">
         <v>19</v>
       </c>
-      <c r="AM4" s="1" t="n">
+      <c r="AM4">
         <v>21</v>
       </c>
-      <c r="AN4" s="1" t="n">
+      <c r="AN4">
         <v>32</v>
       </c>
-      <c r="AO4" s="1" t="n">
+      <c r="AO4">
         <v>11</v>
       </c>
-      <c r="AP4" s="1" t="n">
+      <c r="AP4">
         <v>0</v>
       </c>
-      <c r="AQ4" s="1" t="n">
+      <c r="AQ4">
         <v>19</v>
       </c>
-      <c r="AR4" s="1" t="n">
+      <c r="AR4">
         <v>33</v>
       </c>
-      <c r="AS4" s="1" t="n">
+      <c r="AS4">
         <v>24</v>
       </c>
-      <c r="AT4" s="1" t="n">
+      <c r="AT4">
         <v>32</v>
       </c>
-      <c r="AU4" s="1" t="n">
+      <c r="AU4">
         <v>25</v>
       </c>
-      <c r="AV4" s="1" t="n">
+      <c r="AV4">
         <v>26</v>
       </c>
-      <c r="AW4" s="1" t="n">
+      <c r="AW4">
         <v>18</v>
       </c>
-      <c r="AX4" s="1" t="n">
+      <c r="AX4">
         <v>8</v>
       </c>
-      <c r="AY4" s="1" t="n">
+      <c r="AY4">
         <v>4</v>
       </c>
-      <c r="AZ4" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA4" s="1" t="n">
+      <c r="AZ4">
+        <v>28</v>
+      </c>
+      <c r="BA4">
         <v>7</v>
       </c>
-      <c r="BB4" s="1" t="n">
+      <c r="BB4">
         <v>6</v>
       </c>
-      <c r="BC4" s="1" t="n">
+      <c r="BC4">
         <v>29</v>
       </c>
-      <c r="BE4" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D4:BC4)</f>
+      <c r="BE4">
         <v>439</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="1" t="s">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="G5" s="1" t="n">
+      <c r="F5">
+        <v>28</v>
+      </c>
+      <c r="G5">
         <v>38</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5">
         <v>22</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5">
         <v>22</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5">
         <v>25</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5">
         <v>40</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5">
         <v>8</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5">
         <v>33</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5">
         <v>24</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5">
         <v>34</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="P5">
         <v>35</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="Q5">
         <v>7</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5">
         <v>13</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="S5">
         <v>16</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="T5">
         <v>32</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="U5">
         <v>34</v>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="V5">
         <v>8</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="W5">
         <v>40</v>
       </c>
-      <c r="X5" s="1" t="n">
+      <c r="X5">
         <v>14</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="Y5">
         <v>6</v>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="Z5">
         <v>31</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AA5">
         <v>7</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AC5">
         <v>20</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AD5">
         <v>20</v>
       </c>
-      <c r="AE5" s="1" t="n">
+      <c r="AE5">
         <v>0</v>
       </c>
-      <c r="AF5" s="1" t="n">
+      <c r="AF5">
         <v>13</v>
       </c>
-      <c r="AG5" s="1" t="n">
+      <c r="AG5">
         <v>23</v>
       </c>
-      <c r="AH5" s="6" t="n">
+      <c r="AH5" s="4">
         <v>32</v>
       </c>
-      <c r="AI5" s="1" t="n">
+      <c r="AI5">
         <v>25</v>
       </c>
-      <c r="AJ5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" s="1" t="n">
+      <c r="AJ5">
+        <v>28</v>
+      </c>
+      <c r="AK5">
         <v>16</v>
       </c>
-      <c r="AL5" s="1" t="n">
+      <c r="AL5">
         <v>14</v>
       </c>
-      <c r="AM5" s="1" t="n">
+      <c r="AM5">
         <v>36</v>
       </c>
-      <c r="AN5" s="1" t="n">
+      <c r="AN5">
         <v>31</v>
       </c>
-      <c r="AO5" s="1" t="n">
+      <c r="AO5">
         <v>12</v>
       </c>
-      <c r="AP5" s="1" t="n">
+      <c r="AP5">
         <v>30</v>
       </c>
-      <c r="AQ5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR5" s="1" t="n">
+      <c r="AQ5">
+        <v>28</v>
+      </c>
+      <c r="AR5">
         <v>26</v>
       </c>
-      <c r="AS5" s="1" t="n">
+      <c r="AS5">
         <v>12</v>
       </c>
-      <c r="AT5" s="1" t="n">
+      <c r="AT5">
         <v>8</v>
       </c>
-      <c r="AU5" s="1" t="n">
+      <c r="AU5">
         <v>32</v>
       </c>
-      <c r="AV5" s="1" t="n">
+      <c r="AV5">
         <v>13</v>
       </c>
-      <c r="AW5" s="1" t="n">
+      <c r="AW5">
         <v>36</v>
       </c>
-      <c r="AX5" s="1" t="n">
+      <c r="AX5">
         <v>17</v>
       </c>
-      <c r="AY5" s="1" t="n">
+      <c r="AY5">
         <v>18</v>
       </c>
-      <c r="AZ5" s="1" t="n">
+      <c r="AZ5">
         <v>11</v>
       </c>
-      <c r="BA5" s="1" t="n">
+      <c r="BA5">
         <v>37</v>
       </c>
-      <c r="BB5" s="1" t="n">
+      <c r="BB5">
         <v>12</v>
       </c>
-      <c r="BC5" s="1" t="n">
+      <c r="BC5">
         <v>29</v>
       </c>
-      <c r="BE5" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D5:BC5)</f>
+      <c r="BE5">
         <v>503</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="1" t="s">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6">
         <v>16</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6">
         <v>25</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6">
         <v>24</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6">
         <v>22</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="L6">
         <v>37</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6">
         <v>7</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6">
         <v>11</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6">
         <v>20</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="P6">
         <v>8</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="Q6">
         <v>9</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6">
         <v>29</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="S6">
         <v>40</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="T6">
         <v>15</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="U6">
         <v>3</v>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="V6">
         <v>33</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="W6">
         <v>36</v>
       </c>
-      <c r="X6" s="1" t="n">
+      <c r="X6">
         <v>33</v>
       </c>
-      <c r="Y6" s="1" t="n">
+      <c r="Y6">
         <v>0</v>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="Z6">
         <v>6</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AA6">
         <v>21</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AB6">
         <v>27</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AC6">
         <v>21</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AD6">
         <v>30</v>
       </c>
-      <c r="AE6" s="1" t="n">
+      <c r="AE6">
         <v>0</v>
       </c>
-      <c r="AF6" s="1" t="n">
+      <c r="AF6">
         <v>10</v>
       </c>
-      <c r="AG6" s="1" t="n">
+      <c r="AG6">
         <v>5</v>
       </c>
-      <c r="AH6" s="6" t="n">
+      <c r="AH6" s="4">
         <v>7</v>
       </c>
-      <c r="AI6" s="1" t="n">
+      <c r="AI6">
         <v>31</v>
       </c>
-      <c r="AJ6" s="1" t="n">
+      <c r="AJ6">
         <v>29</v>
       </c>
-      <c r="AK6" s="1" t="n">
+      <c r="AK6">
         <v>15</v>
       </c>
-      <c r="AL6" s="1" t="n">
+      <c r="AL6">
         <v>30</v>
       </c>
-      <c r="AM6" s="1" t="n">
+      <c r="AM6">
         <v>19</v>
       </c>
-      <c r="AN6" s="1" t="n">
+      <c r="AN6">
         <v>5</v>
       </c>
-      <c r="AO6" s="1" t="n">
+      <c r="AO6">
         <v>4</v>
       </c>
-      <c r="AP6" s="1" t="n">
+      <c r="AP6">
         <v>3</v>
       </c>
-      <c r="AQ6" s="1" t="n">
+      <c r="AQ6">
         <v>13</v>
       </c>
-      <c r="AR6" s="1" t="n">
+      <c r="AR6">
         <v>24</v>
       </c>
-      <c r="AS6" s="1" t="n">
+      <c r="AS6">
         <v>15</v>
       </c>
-      <c r="AT6" s="1" t="n">
+      <c r="AT6">
         <v>23</v>
       </c>
-      <c r="AU6" s="1" t="n">
+      <c r="AU6">
         <v>23</v>
       </c>
-      <c r="AV6" s="1" t="n">
+      <c r="AV6">
         <v>35</v>
       </c>
-      <c r="AW6" s="1" t="n">
+      <c r="AW6">
         <v>8</v>
       </c>
-      <c r="AX6" s="1" t="n">
+      <c r="AX6">
         <v>2</v>
       </c>
-      <c r="AY6" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ6" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA6" s="1" t="n">
+      <c r="AY6">
+        <v>28</v>
+      </c>
+      <c r="AZ6">
+        <v>28</v>
+      </c>
+      <c r="BA6">
         <v>9</v>
       </c>
-      <c r="BB6" s="1" t="n">
+      <c r="BB6">
         <v>40</v>
       </c>
-      <c r="BC6" s="1" t="n">
+      <c r="BC6">
         <v>9</v>
       </c>
-      <c r="BE6" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D6:BC6)</f>
+      <c r="BE6">
         <v>400</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="1" t="s">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7">
         <v>12</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7">
         <v>22</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7">
         <v>38</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7">
         <v>27</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7">
         <v>30</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7">
         <v>21</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L7">
         <v>12</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="N7" s="1" t="n">
+      <c r="M7">
+        <v>28</v>
+      </c>
+      <c r="N7">
         <v>15</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7">
         <v>17</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="P7">
         <v>8</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="Q7">
         <v>27</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7">
         <v>16</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="S7">
         <v>18</v>
       </c>
-      <c r="T7" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="U7" s="1" t="n">
+      <c r="T7">
+        <v>28</v>
+      </c>
+      <c r="U7">
         <v>8</v>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="V7">
         <v>3</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="W7">
         <v>21</v>
       </c>
-      <c r="X7" s="1" t="n">
+      <c r="X7">
         <v>3</v>
       </c>
-      <c r="Y7" s="1" t="n">
+      <c r="Y7">
         <v>13</v>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="Z7">
         <v>2</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AA7">
         <v>10</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AB7">
         <v>20</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AC7">
         <v>39</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AD7">
         <v>26</v>
       </c>
-      <c r="AE7" s="1" t="n">
+      <c r="AE7">
         <v>24</v>
       </c>
-      <c r="AF7" s="1" t="n">
+      <c r="AF7">
         <v>16</v>
       </c>
-      <c r="AG7" s="1" t="n">
+      <c r="AG7">
         <v>8</v>
       </c>
-      <c r="AH7" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI7" s="1" t="n">
+      <c r="AH7" s="4">
+        <v>28</v>
+      </c>
+      <c r="AI7">
         <v>5</v>
       </c>
-      <c r="AJ7" s="1" t="n">
+      <c r="AJ7">
         <v>1</v>
       </c>
-      <c r="AK7" s="1" t="n">
+      <c r="AK7">
         <v>18</v>
       </c>
-      <c r="AL7" s="1" t="n">
+      <c r="AL7">
         <v>26</v>
       </c>
-      <c r="AM7" s="1" t="n">
+      <c r="AM7">
         <v>17</v>
       </c>
-      <c r="AN7" s="1" t="n">
+      <c r="AN7">
         <v>5</v>
       </c>
-      <c r="AO7" s="1" t="n">
+      <c r="AO7">
         <v>5</v>
       </c>
-      <c r="AP7" s="1" t="n">
+      <c r="AP7">
         <v>21</v>
       </c>
-      <c r="AQ7" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR7" s="1" t="n">
+      <c r="AQ7">
+        <v>28</v>
+      </c>
+      <c r="AR7">
         <v>33</v>
       </c>
-      <c r="AS7" s="1" t="n">
+      <c r="AS7">
         <v>29</v>
       </c>
-      <c r="AT7" s="1" t="n">
+      <c r="AT7">
         <v>24</v>
       </c>
-      <c r="AU7" s="1" t="n">
+      <c r="AU7">
         <v>18</v>
       </c>
-      <c r="AV7" s="1" t="n">
+      <c r="AV7">
         <v>34</v>
       </c>
-      <c r="AW7" s="1" t="n">
+      <c r="AW7">
         <v>0</v>
       </c>
-      <c r="AX7" s="1" t="n">
+      <c r="AX7">
         <v>32</v>
       </c>
-      <c r="AY7" s="1" t="n">
+      <c r="AY7">
         <v>32</v>
       </c>
-      <c r="AZ7" s="1" t="n">
+      <c r="AZ7">
         <v>7</v>
       </c>
-      <c r="BA7" s="1" t="n">
+      <c r="BA7">
         <v>23</v>
       </c>
-      <c r="BB7" s="1" t="n">
+      <c r="BB7">
         <v>21</v>
       </c>
-      <c r="BC7" s="1" t="n">
+      <c r="BC7">
         <v>17</v>
       </c>
-      <c r="BE7" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D7:BC7)</f>
+      <c r="BE7">
         <v>424</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="1" t="s">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>28</v>
+      </c>
+      <c r="F8">
         <v>33</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8">
         <v>7</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8">
         <v>14</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8">
         <v>20</v>
       </c>
-      <c r="K8" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="L8" s="1" t="n">
+      <c r="K8">
+        <v>28</v>
+      </c>
+      <c r="L8">
         <v>10</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8">
         <v>25</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="N8">
         <v>16</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="O8">
         <v>20</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="P8">
         <v>18</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="Q8">
         <v>25</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="R8">
         <v>11</v>
       </c>
-      <c r="S8" s="1" t="n">
+      <c r="S8">
         <v>36</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="U8" s="1" t="n">
+      <c r="T8">
+        <v>28</v>
+      </c>
+      <c r="U8">
         <v>7</v>
       </c>
-      <c r="V8" s="1" t="n">
+      <c r="V8">
         <v>30</v>
       </c>
-      <c r="W8" s="1" t="n">
+      <c r="W8">
         <v>29</v>
       </c>
-      <c r="X8" s="1" t="n">
+      <c r="X8">
         <v>16</v>
       </c>
-      <c r="Y8" s="1" t="n">
+      <c r="Y8">
         <v>23</v>
       </c>
-      <c r="Z8" s="1" t="n">
+      <c r="Z8">
         <v>14</v>
       </c>
-      <c r="AA8" s="1" t="n">
+      <c r="AA8">
         <v>3</v>
       </c>
-      <c r="AB8" s="1" t="n">
+      <c r="AB8">
         <v>38</v>
       </c>
-      <c r="AC8" s="1" t="n">
+      <c r="AC8">
         <v>31</v>
       </c>
-      <c r="AD8" s="1" t="n">
+      <c r="AD8">
         <v>35</v>
       </c>
-      <c r="AE8" s="1" t="n">
+      <c r="AE8">
         <v>39</v>
       </c>
-      <c r="AF8" s="1" t="n">
+      <c r="AF8">
         <v>16</v>
       </c>
-      <c r="AG8" s="1" t="n">
+      <c r="AG8">
         <v>25</v>
       </c>
-      <c r="AH8" s="6" t="n">
+      <c r="AH8" s="4">
         <v>23</v>
       </c>
-      <c r="AI8" s="1" t="n">
+      <c r="AI8">
         <v>38</v>
       </c>
-      <c r="AJ8" s="1" t="n">
+      <c r="AJ8">
         <v>27</v>
       </c>
-      <c r="AK8" s="1" t="n">
+      <c r="AK8">
         <v>40</v>
       </c>
-      <c r="AL8" s="1" t="n">
+      <c r="AL8">
         <v>0</v>
       </c>
-      <c r="AM8" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AN8" s="1" t="n">
+      <c r="AM8">
+        <v>28</v>
+      </c>
+      <c r="AN8">
         <v>27</v>
       </c>
-      <c r="AO8" s="1" t="n">
+      <c r="AO8">
         <v>15</v>
       </c>
-      <c r="AP8" s="1" t="n">
+      <c r="AP8">
         <v>29</v>
       </c>
-      <c r="AQ8" s="1" t="n">
+      <c r="AQ8">
         <v>13</v>
       </c>
-      <c r="AR8" s="1" t="n">
+      <c r="AR8">
         <v>38</v>
       </c>
-      <c r="AS8" s="1" t="n">
+      <c r="AS8">
         <v>18</v>
       </c>
-      <c r="AT8" s="1" t="n">
+      <c r="AT8">
         <v>9</v>
       </c>
-      <c r="AU8" s="1" t="n">
+      <c r="AU8">
         <v>32</v>
       </c>
-      <c r="AV8" s="1" t="n">
+      <c r="AV8">
         <v>27</v>
       </c>
-      <c r="AW8" s="1" t="n">
+      <c r="AW8">
         <v>3</v>
       </c>
-      <c r="AX8" s="1" t="n">
+      <c r="AX8">
         <v>14</v>
       </c>
-      <c r="AY8" s="1" t="n">
+      <c r="AY8">
         <v>5</v>
       </c>
-      <c r="AZ8" s="1" t="n">
+      <c r="AZ8">
         <v>11</v>
       </c>
-      <c r="BA8" s="1" t="n">
+      <c r="BA8">
         <v>1</v>
       </c>
-      <c r="BB8" s="1" t="n">
+      <c r="BB8">
         <v>8</v>
       </c>
-      <c r="BC8" s="1" t="n">
+      <c r="BC8">
         <v>39</v>
       </c>
-      <c r="BE8" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D8:BC8)</f>
+      <c r="BE8">
         <v>445</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="1" t="s">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9">
         <v>26</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9">
         <v>19</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9">
         <v>27</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9">
         <v>12</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9">
         <v>37</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="K9">
         <v>8</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="L9">
         <v>9</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9">
         <v>23</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="N9">
         <v>27</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O9">
         <v>3</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="P9">
         <v>8</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="Q9">
         <v>40</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="R9">
         <v>17</v>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="S9">
         <v>2</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="U9">
         <v>1</v>
       </c>
-      <c r="V9" s="1" t="n">
+      <c r="V9">
         <v>21</v>
       </c>
-      <c r="W9" s="1" t="n">
+      <c r="W9">
         <v>17</v>
       </c>
-      <c r="X9" s="1" t="n">
+      <c r="X9">
         <v>39</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="Y9">
         <v>39</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="Z9">
         <v>6</v>
       </c>
-      <c r="AA9" s="1" t="n">
+      <c r="AA9">
         <v>16</v>
       </c>
-      <c r="AB9" s="1" t="n">
+      <c r="AB9">
         <v>16</v>
       </c>
-      <c r="AC9" s="1" t="n">
+      <c r="AC9">
         <v>17</v>
       </c>
-      <c r="AD9" s="1" t="n">
+      <c r="AD9">
         <v>2</v>
       </c>
-      <c r="AE9" s="1" t="n">
+      <c r="AE9">
         <v>39</v>
       </c>
-      <c r="AF9" s="1" t="n">
+      <c r="AF9">
         <v>36</v>
       </c>
-      <c r="AG9" s="1" t="n">
+      <c r="AG9">
         <v>37</v>
       </c>
-      <c r="AH9" s="6" t="n">
+      <c r="AH9" s="4">
         <v>10</v>
       </c>
-      <c r="AI9" s="1" t="n">
+      <c r="AI9">
         <v>7</v>
       </c>
-      <c r="AJ9" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK9" s="1" t="n">
+      <c r="AJ9">
+        <v>28</v>
+      </c>
+      <c r="AK9">
         <v>14</v>
       </c>
-      <c r="AL9" s="1" t="n">
+      <c r="AL9">
         <v>6</v>
       </c>
-      <c r="AM9" s="1" t="n">
+      <c r="AM9">
         <v>33</v>
       </c>
-      <c r="AN9" s="1" t="n">
+      <c r="AN9">
         <v>33</v>
       </c>
-      <c r="AO9" s="1" t="n">
+      <c r="AO9">
         <v>13</v>
       </c>
-      <c r="AP9" s="1" t="n">
+      <c r="AP9">
         <v>39</v>
       </c>
-      <c r="AQ9" s="1" t="n">
+      <c r="AQ9">
         <v>1</v>
       </c>
-      <c r="AR9" s="1" t="n">
+      <c r="AR9">
         <v>7</v>
       </c>
-      <c r="AS9" s="1" t="n">
+      <c r="AS9">
         <v>35</v>
       </c>
-      <c r="AT9" s="1" t="n">
+      <c r="AT9">
         <v>9</v>
       </c>
-      <c r="AU9" s="1" t="n">
+      <c r="AU9">
         <v>27</v>
       </c>
-      <c r="AV9" s="1" t="n">
+      <c r="AV9">
         <v>17</v>
       </c>
-      <c r="AW9" s="1" t="n">
+      <c r="AW9">
         <v>15</v>
       </c>
-      <c r="AX9" s="1" t="n">
+      <c r="AX9">
         <v>17</v>
       </c>
-      <c r="AY9" s="1" t="n">
+      <c r="AY9">
         <v>39</v>
       </c>
-      <c r="AZ9" s="1" t="n">
+      <c r="AZ9">
         <v>21</v>
       </c>
-      <c r="BA9" s="1" t="n">
+      <c r="BA9">
         <v>37</v>
       </c>
-      <c r="BB9" s="1" t="n">
+      <c r="BB9">
         <v>40</v>
       </c>
-      <c r="BC9" s="1" t="n">
+      <c r="BC9">
         <v>22</v>
       </c>
-      <c r="BE9" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D9:BC9)</f>
-        <v>470</v>
-      </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="1" t="s">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10">
         <v>25</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10">
         <v>23</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10">
         <v>33</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10">
         <v>40</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10">
         <v>9</v>
       </c>
-      <c r="J10" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="K10" s="1" t="n">
+      <c r="J10">
+        <v>28</v>
+      </c>
+      <c r="K10">
         <v>35</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="L10">
         <v>6</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10">
         <v>7</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10">
         <v>37</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10">
         <v>21</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="P10">
         <v>6</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="Q10">
         <v>7</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10">
         <v>3</v>
       </c>
-      <c r="S10" s="1" t="n">
+      <c r="S10">
         <v>6</v>
       </c>
-      <c r="T10" s="1" t="n">
+      <c r="T10">
         <v>40</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="U10">
         <v>29</v>
       </c>
-      <c r="V10" s="1" t="n">
+      <c r="V10">
         <v>38</v>
       </c>
-      <c r="W10" s="1" t="n">
+      <c r="W10">
         <v>35</v>
       </c>
-      <c r="X10" s="1" t="n">
+      <c r="X10">
         <v>0</v>
       </c>
-      <c r="Y10" s="1" t="n">
+      <c r="Y10">
         <v>34</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="Z10">
         <v>10</v>
       </c>
-      <c r="AA10" s="1" t="n">
+      <c r="AA10">
         <v>13</v>
       </c>
-      <c r="AB10" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AB10">
+        <v>28</v>
+      </c>
+      <c r="AC10">
         <v>25</v>
       </c>
-      <c r="AD10" s="1" t="n">
+      <c r="AD10">
         <v>20</v>
       </c>
-      <c r="AE10" s="1" t="n">
+      <c r="AE10">
         <v>4</v>
       </c>
-      <c r="AF10" s="1" t="n">
+      <c r="AF10">
         <v>24</v>
       </c>
-      <c r="AG10" s="1" t="n">
+      <c r="AG10">
         <v>39</v>
       </c>
-      <c r="AH10" s="6" t="n">
+      <c r="AH10" s="4">
         <v>18</v>
       </c>
-      <c r="AI10" s="1" t="n">
+      <c r="AI10">
         <v>18</v>
       </c>
-      <c r="AJ10" s="1" t="n">
+      <c r="AJ10">
         <v>36</v>
       </c>
-      <c r="AK10" s="1" t="n">
+      <c r="AK10">
         <v>33</v>
       </c>
-      <c r="AL10" s="1" t="n">
+      <c r="AL10">
         <v>21</v>
       </c>
-      <c r="AM10" s="1" t="n">
+      <c r="AM10">
         <v>9</v>
       </c>
-      <c r="AN10" s="1" t="n">
+      <c r="AN10">
         <v>34</v>
       </c>
-      <c r="AO10" s="1" t="n">
+      <c r="AO10">
         <v>13</v>
       </c>
-      <c r="AP10" s="1" t="n">
+      <c r="AP10">
         <v>7</v>
       </c>
-      <c r="AQ10" s="1" t="n">
+      <c r="AQ10">
         <v>6</v>
       </c>
-      <c r="AR10" s="1" t="n">
+      <c r="AR10">
         <v>13</v>
       </c>
-      <c r="AS10" s="1" t="n">
+      <c r="AS10">
         <v>27</v>
       </c>
-      <c r="AT10" s="1" t="n">
+      <c r="AT10">
         <v>16</v>
       </c>
-      <c r="AU10" s="1" t="n">
+      <c r="AU10">
         <v>16</v>
       </c>
-      <c r="AV10" s="1" t="n">
+      <c r="AV10">
         <v>19</v>
       </c>
-      <c r="AW10" s="1" t="n">
+      <c r="AW10">
         <v>35</v>
       </c>
-      <c r="AX10" s="1" t="n">
+      <c r="AX10">
         <v>15</v>
       </c>
-      <c r="AY10" s="1" t="n">
+      <c r="AY10">
         <v>25</v>
       </c>
-      <c r="AZ10" s="1" t="n">
+      <c r="AZ10">
         <v>10</v>
       </c>
-      <c r="BA10" s="1" t="n">
+      <c r="BA10">
         <v>31</v>
       </c>
-      <c r="BB10" s="1" t="n">
+      <c r="BB10">
         <v>9</v>
       </c>
-      <c r="BC10" s="1" t="n">
+      <c r="BC10">
         <v>22</v>
       </c>
-      <c r="BE10" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D10:BC10)</f>
-        <v>433</v>
-      </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="1" t="s">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11">
         <v>40</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11">
         <v>7</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11">
         <v>21</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11">
         <v>6</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="K11">
         <v>3</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="L11">
         <v>5</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11">
         <v>11</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="N11">
         <v>13</v>
       </c>
-      <c r="O11" s="1" t="n">
+      <c r="O11">
         <v>20</v>
       </c>
-      <c r="P11" s="1" t="n">
+      <c r="P11">
         <v>11</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="Q11">
         <v>30</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11">
         <v>15</v>
       </c>
-      <c r="S11" s="1" t="n">
+      <c r="S11">
         <v>14</v>
       </c>
-      <c r="T11" s="1" t="n">
+      <c r="T11">
         <v>37</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="U11">
         <v>34</v>
       </c>
-      <c r="V11" s="1" t="n">
+      <c r="V11">
         <v>35</v>
       </c>
-      <c r="W11" s="1" t="n">
+      <c r="W11">
         <v>40</v>
       </c>
-      <c r="X11" s="1" t="n">
+      <c r="X11">
         <v>8</v>
       </c>
-      <c r="Y11" s="1" t="n">
+      <c r="Y11">
         <v>24</v>
       </c>
-      <c r="Z11" s="1" t="n">
+      <c r="Z11">
         <v>20</v>
       </c>
-      <c r="AA11" s="1" t="n">
+      <c r="AA11">
         <v>36</v>
       </c>
-      <c r="AB11" s="1" t="n">
+      <c r="AB11">
         <v>14</v>
       </c>
-      <c r="AC11" s="1" t="n">
+      <c r="AC11">
         <v>9</v>
       </c>
-      <c r="AD11" s="1" t="n">
+      <c r="AD11">
         <v>12</v>
       </c>
-      <c r="AE11" s="1" t="n">
+      <c r="AE11">
         <v>11</v>
       </c>
-      <c r="AF11" s="1" t="n">
+      <c r="AF11">
         <v>2</v>
       </c>
-      <c r="AG11" s="1" t="n">
+      <c r="AG11">
         <v>39</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="4">
         <v>29</v>
       </c>
-      <c r="AI11" s="1" t="n">
+      <c r="AI11">
         <v>34</v>
       </c>
-      <c r="AJ11" s="1" t="n">
+      <c r="AJ11">
         <v>25</v>
       </c>
-      <c r="AK11" s="1" t="n">
+      <c r="AK11">
         <v>33</v>
       </c>
-      <c r="AL11" s="1" t="n">
+      <c r="AL11">
         <v>7</v>
       </c>
-      <c r="AM11" s="1" t="n">
+      <c r="AM11">
         <v>12</v>
       </c>
-      <c r="AN11" s="1" t="n">
+      <c r="AN11">
         <v>22</v>
       </c>
-      <c r="AO11" s="1" t="n">
+      <c r="AO11">
         <v>26</v>
       </c>
-      <c r="AP11" s="1" t="n">
+      <c r="AP11">
         <v>26</v>
       </c>
-      <c r="AQ11" s="1" t="n">
+      <c r="AQ11">
         <v>40</v>
       </c>
-      <c r="AR11" s="1" t="n">
+      <c r="AR11">
         <v>7</v>
       </c>
-      <c r="AS11" s="1" t="n">
+      <c r="AS11">
         <v>30</v>
       </c>
-      <c r="AT11" s="1" t="n">
+      <c r="AT11">
         <v>39</v>
       </c>
-      <c r="AU11" s="1" t="n">
+      <c r="AU11">
         <v>17</v>
       </c>
-      <c r="AV11" s="1" t="n">
+      <c r="AV11">
         <v>30</v>
       </c>
-      <c r="AW11" s="1" t="n">
+      <c r="AW11">
         <v>4</v>
       </c>
-      <c r="AX11" s="1" t="n">
+      <c r="AX11">
         <v>25</v>
       </c>
-      <c r="AY11" s="1" t="n">
+      <c r="AY11">
         <v>34</v>
       </c>
-      <c r="AZ11" s="1" t="n">
+      <c r="AZ11">
         <v>25</v>
       </c>
-      <c r="BA11" s="1" t="n">
+      <c r="BA11">
         <v>5</v>
       </c>
-      <c r="BB11" s="1" t="n">
+      <c r="BB11">
         <v>5</v>
       </c>
-      <c r="BC11" s="1" t="n">
+      <c r="BC11">
         <v>2</v>
       </c>
-      <c r="BE11" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D11:BC11)</f>
-        <v>477</v>
-      </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="1" t="s">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12">
         <v>27</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12">
         <v>27</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H12" s="1" t="n">
+      <c r="G12">
+        <v>28</v>
+      </c>
+      <c r="H12">
         <v>20</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I12">
         <v>26</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12">
         <v>5</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="K12">
         <v>24</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="L12">
         <v>2</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12">
         <v>22</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="N12">
         <v>7</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="O12">
         <v>22</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="P12">
         <v>15</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="Q12">
         <v>25</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12">
         <v>18</v>
       </c>
-      <c r="S12" s="1" t="n">
+      <c r="S12">
         <v>37</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="T12">
         <v>38</v>
       </c>
-      <c r="U12" s="1" t="n">
+      <c r="U12">
         <v>23</v>
       </c>
-      <c r="V12" s="1" t="n">
+      <c r="V12">
         <v>9</v>
       </c>
-      <c r="W12" s="1" t="n">
+      <c r="W12">
         <v>31</v>
       </c>
-      <c r="X12" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y12" s="1" t="n">
+      <c r="X12">
+        <v>28</v>
+      </c>
+      <c r="Y12">
         <v>2</v>
       </c>
-      <c r="Z12" s="1" t="n">
+      <c r="Z12">
         <v>10</v>
       </c>
-      <c r="AA12" s="1" t="n">
+      <c r="AA12">
         <v>13</v>
       </c>
-      <c r="AB12" s="1" t="n">
+      <c r="AB12">
         <v>12</v>
       </c>
-      <c r="AC12" s="1" t="n">
+      <c r="AC12">
         <v>40</v>
       </c>
-      <c r="AD12" s="1" t="n">
+      <c r="AD12">
         <v>36</v>
       </c>
-      <c r="AE12" s="1" t="n">
+      <c r="AE12">
         <v>35</v>
       </c>
-      <c r="AF12" s="1" t="n">
+      <c r="AF12">
         <v>33</v>
       </c>
-      <c r="AG12" s="1" t="n">
+      <c r="AG12">
         <v>35</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="4">
         <v>13</v>
       </c>
-      <c r="AI12" s="1" t="n">
+      <c r="AI12">
         <v>27</v>
       </c>
-      <c r="AJ12" s="1" t="n">
+      <c r="AJ12">
         <v>12</v>
       </c>
-      <c r="AK12" s="1" t="n">
+      <c r="AK12">
         <v>19</v>
       </c>
-      <c r="AL12" s="1" t="n">
+      <c r="AL12">
         <v>30</v>
       </c>
-      <c r="AM12" s="1" t="n">
+      <c r="AM12">
         <v>4</v>
       </c>
-      <c r="AN12" s="1" t="n">
+      <c r="AN12">
         <v>3</v>
       </c>
-      <c r="AO12" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP12" s="1" t="n">
+      <c r="AO12">
+        <v>28</v>
+      </c>
+      <c r="AP12">
         <v>14</v>
       </c>
-      <c r="AQ12" s="1" t="n">
+      <c r="AQ12">
         <v>11</v>
       </c>
-      <c r="AR12" s="1" t="n">
+      <c r="AR12">
         <v>12</v>
       </c>
-      <c r="AS12" s="1" t="n">
+      <c r="AS12">
         <v>4</v>
       </c>
-      <c r="AT12" s="1" t="n">
+      <c r="AT12">
         <v>4</v>
       </c>
-      <c r="AU12" s="1" t="n">
+      <c r="AU12">
         <v>2</v>
       </c>
-      <c r="AV12" s="1" t="n">
+      <c r="AV12">
         <v>1</v>
       </c>
-      <c r="AW12" s="1" t="n">
+      <c r="AW12">
         <v>11</v>
       </c>
-      <c r="AX12" s="1" t="n">
+      <c r="AX12">
         <v>15</v>
       </c>
-      <c r="AY12" s="1" t="n">
+      <c r="AY12">
         <v>16</v>
       </c>
-      <c r="AZ12" s="1" t="n">
+      <c r="AZ12">
         <v>27</v>
       </c>
-      <c r="BA12" s="1" t="n">
+      <c r="BA12">
         <v>11</v>
       </c>
-      <c r="BB12" s="1" t="n">
+      <c r="BB12">
         <v>17</v>
       </c>
-      <c r="BC12" s="1" t="n">
+      <c r="BC12">
         <v>24</v>
       </c>
-      <c r="BE12" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D12:BC12)</f>
-        <v>305</v>
-      </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="1" t="s">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="E13">
         <v>36</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13">
         <v>11</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13">
         <v>9</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13">
         <v>17</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I13">
         <v>38</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13">
         <v>29</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="K13">
         <v>2</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="L13">
         <v>30</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13">
         <v>24</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N13">
         <v>2</v>
       </c>
-      <c r="O13" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="P13" s="1" t="n">
+      <c r="O13">
+        <v>28</v>
+      </c>
+      <c r="P13">
         <v>4</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="Q13">
         <v>29</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="R13">
         <v>21</v>
       </c>
-      <c r="S13" s="1" t="n">
+      <c r="S13">
         <v>8</v>
       </c>
-      <c r="T13" s="1" t="n">
+      <c r="T13">
         <v>18</v>
       </c>
-      <c r="U13" s="1" t="n">
+      <c r="U13">
         <v>3</v>
       </c>
-      <c r="V13" s="1" t="n">
+      <c r="V13">
         <v>37</v>
       </c>
-      <c r="W13" s="1" t="n">
+      <c r="W13">
         <v>18</v>
       </c>
-      <c r="X13" s="1" t="n">
+      <c r="X13">
         <v>19</v>
       </c>
-      <c r="Y13" s="1" t="n">
+      <c r="Y13">
         <v>1</v>
       </c>
-      <c r="Z13" s="1" t="n">
+      <c r="Z13">
         <v>16</v>
       </c>
-      <c r="AA13" s="1" t="n">
+      <c r="AA13">
         <v>13</v>
       </c>
-      <c r="AB13" s="1" t="n">
+      <c r="AB13">
         <v>39</v>
       </c>
-      <c r="AC13" s="1" t="n">
+      <c r="AC13">
         <v>31</v>
       </c>
-      <c r="AD13" s="1" t="n">
+      <c r="AD13">
         <v>19</v>
       </c>
-      <c r="AE13" s="1" t="n">
+      <c r="AE13">
         <v>33</v>
       </c>
-      <c r="AF13" s="1" t="n">
+      <c r="AF13">
         <v>39</v>
       </c>
-      <c r="AG13" s="1" t="n">
+      <c r="AG13">
         <v>30</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="4">
         <v>23</v>
       </c>
-      <c r="AI13" s="1" t="n">
+      <c r="AI13">
         <v>37</v>
       </c>
-      <c r="AJ13" s="1" t="n">
+      <c r="AJ13">
         <v>22</v>
       </c>
-      <c r="AK13" s="1" t="n">
+      <c r="AK13">
         <v>16</v>
       </c>
-      <c r="AL13" s="1" t="n">
+      <c r="AL13">
         <v>27</v>
       </c>
-      <c r="AM13" s="1" t="n">
+      <c r="AM13">
         <v>27</v>
       </c>
-      <c r="AN13" s="1" t="n">
+      <c r="AN13">
         <v>13</v>
       </c>
-      <c r="AO13" s="1" t="n">
+      <c r="AO13">
         <v>17</v>
       </c>
-      <c r="AP13" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ13" s="1" t="n">
+      <c r="AP13">
+        <v>28</v>
+      </c>
+      <c r="AQ13">
         <v>13</v>
       </c>
-      <c r="AR13" s="1" t="n">
+      <c r="AR13">
         <v>2</v>
       </c>
-      <c r="AS13" s="1" t="n">
+      <c r="AS13">
         <v>33</v>
       </c>
-      <c r="AT13" s="1" t="n">
+      <c r="AT13">
         <v>32</v>
       </c>
-      <c r="AU13" s="1" t="n">
+      <c r="AU13">
         <v>37</v>
       </c>
-      <c r="AV13" s="1" t="n">
+      <c r="AV13">
         <v>1</v>
       </c>
-      <c r="AW13" s="1" t="n">
+      <c r="AW13">
         <v>25</v>
       </c>
-      <c r="AX13" s="1" t="n">
+      <c r="AX13">
         <v>18</v>
       </c>
-      <c r="AY13" s="1" t="n">
+      <c r="AY13">
         <v>18</v>
       </c>
-      <c r="AZ13" s="1" t="n">
+      <c r="AZ13">
         <v>5</v>
       </c>
-      <c r="BA13" s="1" t="n">
+      <c r="BA13">
         <v>37</v>
       </c>
-      <c r="BB13" s="1" t="n">
+      <c r="BB13">
         <v>29</v>
       </c>
-      <c r="BC13" s="1" t="n">
+      <c r="BC13">
         <v>3</v>
       </c>
-      <c r="BE13" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D13:BC13)</f>
-        <v>463</v>
-      </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="1" t="s">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14">
         <v>12</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14">
         <v>37</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14">
         <v>8</v>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="I14">
         <v>34</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14">
         <v>8</v>
       </c>
-      <c r="K14" s="1" t="n">
+      <c r="K14">
         <v>25</v>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="L14">
         <v>32</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14">
         <v>12</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="N14">
         <v>2</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="O14">
         <v>30</v>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="P14">
         <v>17</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="Q14">
         <v>9</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="R14">
         <v>11</v>
       </c>
-      <c r="S14" s="1" t="n">
+      <c r="S14">
         <v>24</v>
       </c>
-      <c r="T14" s="1" t="n">
+      <c r="T14">
         <v>14</v>
       </c>
-      <c r="U14" s="1" t="n">
+      <c r="U14">
         <v>40</v>
       </c>
-      <c r="V14" s="1" t="n">
+      <c r="V14">
         <v>9</v>
       </c>
-      <c r="W14" s="1" t="n">
+      <c r="W14">
         <v>20</v>
       </c>
-      <c r="X14" s="1" t="n">
+      <c r="X14">
         <v>36</v>
       </c>
-      <c r="Y14" s="1" t="n">
+      <c r="Y14">
         <v>40</v>
       </c>
-      <c r="Z14" s="1" t="n">
+      <c r="Z14">
         <v>17</v>
       </c>
-      <c r="AA14" s="1" t="n">
+      <c r="AA14">
         <v>14</v>
       </c>
-      <c r="AB14" s="1" t="n">
+      <c r="AB14">
         <v>32</v>
       </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AC14">
         <v>10</v>
       </c>
-      <c r="AD14" s="1" t="n">
+      <c r="AD14">
         <v>26</v>
       </c>
-      <c r="AE14" s="1" t="n">
+      <c r="AE14">
         <v>20</v>
       </c>
-      <c r="AF14" s="1" t="n">
+      <c r="AF14">
         <v>15</v>
       </c>
-      <c r="AG14" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AG14">
+        <v>28</v>
+      </c>
+      <c r="AH14" s="4">
         <v>22</v>
       </c>
-      <c r="AI14" s="1" t="n">
+      <c r="AI14">
         <v>15</v>
       </c>
-      <c r="AJ14" s="1" t="n">
+      <c r="AJ14">
         <v>39</v>
       </c>
-      <c r="AK14" s="1" t="n">
+      <c r="AK14">
         <v>19</v>
       </c>
-      <c r="AL14" s="1" t="n">
+      <c r="AL14">
         <v>10</v>
       </c>
-      <c r="AM14" s="1" t="n">
+      <c r="AM14">
         <v>30</v>
       </c>
-      <c r="AN14" s="1" t="n">
+      <c r="AN14">
         <v>13</v>
       </c>
-      <c r="AO14" s="1" t="n">
+      <c r="AO14">
         <v>8</v>
       </c>
-      <c r="AP14" s="1" t="n">
+      <c r="AP14">
         <v>13</v>
       </c>
-      <c r="AQ14" s="1" t="n">
+      <c r="AQ14">
         <v>25</v>
       </c>
-      <c r="AR14" s="1" t="n">
+      <c r="AR14">
         <v>2</v>
       </c>
-      <c r="AS14" s="1" t="n">
+      <c r="AS14">
         <v>39</v>
       </c>
-      <c r="AT14" s="1" t="n">
+      <c r="AT14">
         <v>5</v>
       </c>
-      <c r="AU14" s="1" t="n">
+      <c r="AU14">
         <v>0</v>
       </c>
-      <c r="AV14" s="1" t="n">
+      <c r="AV14">
         <v>26</v>
       </c>
-      <c r="AW14" s="1" t="n">
+      <c r="AW14">
         <v>32</v>
       </c>
-      <c r="AX14" s="1" t="n">
+      <c r="AX14">
         <v>36</v>
       </c>
-      <c r="AY14" s="1" t="n">
+      <c r="AY14">
         <v>25</v>
       </c>
-      <c r="AZ14" s="1" t="n">
+      <c r="AZ14">
         <v>32</v>
       </c>
-      <c r="BA14" s="1" t="n">
+      <c r="BA14">
         <v>19</v>
       </c>
-      <c r="BB14" s="1" t="n">
+      <c r="BB14">
         <v>27</v>
       </c>
-      <c r="BC14" s="1" t="n">
+      <c r="BC14">
         <v>4</v>
-      </c>
-      <c r="BE14" s="1" t="n">
-        <f aca="false">SUMIF(D$2:BC$2,"&gt;="&amp;$B$2,D14:BC14)</f>
-        <v>441</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:BC1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>